--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104618_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104618_W18.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4898</v>
+        <v>7.0222</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9133</v>
+        <v>6.1616</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5764</v>
+        <v>0.8607</v>
       </c>
       <c r="G2" t="n">
-        <v>4.576</v>
+        <v>5.1524</v>
       </c>
       <c r="H2" t="n">
-        <v>1.596</v>
+        <v>1.0421</v>
       </c>
       <c r="I2" t="n">
-        <v>2.98</v>
+        <v>4.1103</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7513</v>
+        <v>6.127</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2268</v>
+        <v>1.6892</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5246</v>
+        <v>4.4377</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8247</v>
+        <v>-0.9745</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6308</v>
+        <v>-0.6471</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4555</v>
+        <v>-0.3275</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4077</v>
+        <v>0.0487</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1179</v>
+        <v>0.0346</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2898</v>
+        <v>0.0141</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4141</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4141</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0523</v>
+        <v>6.7963</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4686</v>
+        <v>3.941</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5836</v>
+        <v>2.8553</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1685</v>
+        <v>4.569</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0345</v>
+        <v>1.5914</v>
       </c>
       <c r="I3" t="n">
-        <v>4.134</v>
+        <v>2.9776</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1642</v>
+        <v>3.7209</v>
       </c>
       <c r="K3" t="n">
-        <v>1.697</v>
+        <v>2.2096</v>
       </c>
       <c r="L3" t="n">
-        <v>4.4672</v>
+        <v>1.5114</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9957</v>
+        <v>0.8481</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6626</v>
+        <v>-0.6182</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3331</v>
+        <v>1.4663</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.0882</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6956</v>
+        <v>-0.0468</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2353</v>
+        <v>-0.0414</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5998</v>
+        <v>6.0021</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2333</v>
+        <v>4.3858</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3665</v>
+        <v>1.6162</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6027</v>
+        <v>3.5899</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1155</v>
+        <v>-0.1095</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7183</v>
+        <v>3.6994</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1425</v>
+        <v>4.1051</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7202</v>
+        <v>0.71</v>
       </c>
       <c r="L4" t="n">
-        <v>3.4223</v>
+        <v>3.3951</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.5152</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0445</v>
+        <v>0.3635</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0907</v>
+        <v>0.2808</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1352</v>
+        <v>0.0827</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5116</v>
+        <v>4.5253</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5767</v>
+        <v>3.282</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9350000000000001</v>
+        <v>1.2432</v>
       </c>
       <c r="G5" t="n">
-        <v>0.334</v>
+        <v>0.336</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8384</v>
+        <v>-1.8327</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1724</v>
+        <v>2.1687</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1565</v>
+        <v>1.1382</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1917</v>
+        <v>-1.2001</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3482</v>
+        <v>2.3383</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8225</v>
+        <v>-0.8022</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8223</v>
+        <v>0.1892</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7652</v>
+        <v>-0.0351</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0572</v>
+        <v>0.2243</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0366</v>
+        <v>2.9822</v>
       </c>
       <c r="E6" t="n">
-        <v>3.002</v>
+        <v>2.0999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0346</v>
+        <v>0.8823</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7528</v>
+        <v>3.2818</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2712</v>
+        <v>-0.7873</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4816</v>
+        <v>4.0691</v>
       </c>
       <c r="J6" t="n">
-        <v>4.8899</v>
+        <v>2.2325</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3897</v>
+        <v>-0.6862</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5002</v>
+        <v>2.9187</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1371</v>
+        <v>1.0493</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1185</v>
+        <v>-0.1011</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0186</v>
+        <v>1.1504</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.4025</v>
+        <v>1.3658</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.5367</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5936</v>
+        <v>-0.5759</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9417</v>
+        <v>-0.1326</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3481</v>
+        <v>-0.4433</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.622</v>
+        <v>2.4627</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1122</v>
+        <v>0.9377</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5098</v>
+        <v>1.525</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5623</v>
+        <v>0.5627</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2986</v>
+        <v>-0.3014</v>
       </c>
       <c r="I7" t="n">
-        <v>0.861</v>
+        <v>0.8641</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6736</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.599</v>
+        <v>0.5893</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6986</v>
+        <v>0.5342</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4386</v>
+        <v>0.2739</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2601</v>
+        <v>0.2603</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>X. LOPEZ-AROSTEGUI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2458</v>
+        <v>2.2947</v>
       </c>
       <c r="E8" t="n">
-        <v>1.701</v>
+        <v>-0.8077</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5449000000000001</v>
+        <v>3.1024</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2871</v>
+        <v>1.0546</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7937</v>
+        <v>0.2637</v>
       </c>
       <c r="I8" t="n">
-        <v>4.0808</v>
+        <v>0.791</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2574</v>
+        <v>0.6948</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6825</v>
+        <v>0.8963</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9399</v>
+        <v>-0.2015</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0297</v>
+        <v>0.3598</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1113</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1409</v>
+        <v>0.9925</v>
       </c>
       <c r="P8" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>2.7316</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3096</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5565</v>
+        <v>-0.2442</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7531</v>
+        <v>0.1688</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>0.8603</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.018</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.1441</v>
+        <v>2.1842</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3108</v>
+        <v>2.0963</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4549</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.843</v>
+        <v>3.7555</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1385</v>
+        <v>1.2723</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2955</v>
+        <v>2.4833</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9313</v>
+        <v>4.8736</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.3418</v>
+        <v>2.3787</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4105</v>
+        <v>2.4949</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0883</v>
+        <v>-1.118</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2033</v>
+        <v>-1.1064</v>
       </c>
       <c r="O9" t="n">
-        <v>0.885</v>
+        <v>-0.0116</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-4.5526</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3727</v>
+        <v>0.7537</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5939</v>
+        <v>1.0728</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7788</v>
+        <v>-0.3191</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.7025</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="10">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6554</v>
+        <v>1.6858</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4012</v>
+        <v>-1.0521</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0567</v>
+        <v>2.7379</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.039</v>
+        <v>-0.0415</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6797</v>
+        <v>-0.6792</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4554</v>
+        <v>-0.4735</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8934</v>
+        <v>0.8823</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3488</v>
+        <v>-1.3559</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4165</v>
+        <v>0.432</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>0.082</v>
+        <v>0.1127</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9043</v>
+        <v>-0.5298</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9863</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X. LOPEZ-AROSTEGUI</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5318</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5052</v>
+        <v>0.1173</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0371</v>
+        <v>0.4829</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0455</v>
+        <v>-0.4102</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2538</v>
+        <v>0.7724</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7917</v>
+        <v>-1.1826</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7085</v>
+        <v>0.0315</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9005</v>
+        <v>0.6722</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.192</v>
+        <v>-0.6407</v>
       </c>
       <c r="M11" t="n">
-        <v>0.337</v>
+        <v>-0.4417</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9837</v>
+        <v>-0.5419</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.722</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8351</v>
+        <v>0.0999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9739</v>
+        <v>0.0858</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1388</v>
+        <v>0.0141</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8678</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0285</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9996</v>
+        <v>0.3355</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4073</v>
+        <v>-2.6719</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5923</v>
+        <v>3.0074</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4171</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.769</v>
+        <v>-2.1369</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1861</v>
+        <v>1.3007</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0383</v>
+        <v>-1.9421</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6754</v>
+        <v>-2.3517</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6371</v>
+        <v>0.4096</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4554</v>
+        <v>1.1058</v>
       </c>
       <c r="N12" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.2148</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.549</v>
+        <v>0.8911</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5093</v>
+        <v>0.5587</v>
       </c>
       <c r="T12" t="n">
-        <v>0.369</v>
+        <v>0.2505</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1403</v>
+        <v>0.3082</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9397</v>
+        <v>-0.8985</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5958</v>
+        <v>-0.1359</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3439</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1764</v>
+        <v>0.1773</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5642</v>
+        <v>-1.5625</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7406</v>
+        <v>1.7398</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2</v>
+        <v>-0.2098</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4688</v>
+        <v>-1.4759</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3764</v>
+        <v>0.3871</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>0.228</v>
+        <v>0.2625</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5565</v>
+        <v>-0.0838</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7845</v>
+        <v>0.3463</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>34.94909999999999</v>
+        <v>35.9928</v>
       </c>
       <c r="E14" t="n">
-        <v>17.6014</v>
+        <v>18.354</v>
       </c>
       <c r="F14" t="n">
-        <v>17.3479</v>
+        <v>17.6387</v>
       </c>
       <c r="G14" t="n">
-        <v>21.2062</v>
+        <v>21.1913</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1837</v>
+        <v>-1.1506</v>
       </c>
       <c r="I14" t="n">
-        <v>22.3901</v>
+        <v>22.34219999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>21.1955</v>
+        <v>20.962</v>
       </c>
       <c r="K14" t="n">
-        <v>4.417199999999999</v>
+        <v>4.313699999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>16.7784</v>
+        <v>16.6482</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01080000000000048</v>
+        <v>0.2293999999999994</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.600899999999999</v>
+        <v>-5.4643</v>
       </c>
       <c r="O14" t="n">
-        <v>5.6117</v>
+        <v>5.694099999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>9.073400000000001</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.2076</v>
+        <v>-10.2435</v>
       </c>
       <c r="R14" t="n">
-        <v>19.2809</v>
+        <v>19.3489</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1341</v>
+        <v>2.1836</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1360000000000001</v>
+        <v>0.9261</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2701</v>
+        <v>1.2576</v>
       </c>
       <c r="V14" t="n">
-        <v>3.5353</v>
+        <v>3.5125</v>
       </c>
       <c r="W14" t="n">
-        <v>6.7491</v>
+        <v>6.709499999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.2138</v>
+        <v>-3.197</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6534</v>
+        <v>0.5386</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4152</v>
+        <v>-0.5457</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0686</v>
+        <v>1.0843</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0925</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5584</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4744</v>
+        <v>-0.4674</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1612</v>
+        <v>0.1607</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6109</v>
+        <v>0.4947</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4386</v>
+        <v>0.3227</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1724</v>
+        <v>0.1721</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>P. RIOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6201</v>
+        <v>-1.6657</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9616</v>
+        <v>-1.3732</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5818</v>
+        <v>-0.2925</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.774</v>
+        <v>-1.4903</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0202</v>
+        <v>-1.4903</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7539</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7121</v>
+        <v>-1.3035</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-1.3035</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7782</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4861</v>
+        <v>-0.1868</v>
       </c>
       <c r="N16" t="n">
-        <v>0.046</v>
+        <v>-0.1868</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.5321</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9536</v>
+        <v>-0.1754</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7693</v>
+        <v>-0.0697</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8157</v>
+        <v>-0.1057</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. RIOS</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6907</v>
+        <v>-1.8854</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3652</v>
+        <v>-0.8531</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3255</v>
+        <v>-1.0323</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4847</v>
+        <v>-3.1186</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4847</v>
+        <v>-2.0451</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-1.0735</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2956</v>
+        <v>-0.6575</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2956</v>
+        <v>-1.0967</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.4392</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1891</v>
+        <v>-2.4612</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1891</v>
+        <v>-0.9485</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-1.5127</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.206</v>
+        <v>0.165</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0696</v>
+        <v>-0.3534</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1364</v>
+        <v>0.5184</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9491</v>
+        <v>-1.941</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0718</v>
+        <v>-0.7236</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8773</v>
+        <v>-1.2174</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.1338</v>
+        <v>-2.2672</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0491</v>
+        <v>-1.2322</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0848</v>
+        <v>-1.035</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6428</v>
+        <v>-0.649</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0878</v>
+        <v>-0.6862</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4451</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4911</v>
+        <v>-1.6182</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.546</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5299</v>
+        <v>-1.0722</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1167</v>
+        <v>-0.129</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5898</v>
+        <v>-0.0746</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7065</v>
+        <v>-0.0545</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,22 +1891,22 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1232</v>
+        <v>-2.125</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2037</v>
+        <v>-1.2079</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9195</v>
+        <v>-0.9171</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7622</v>
+        <v>-0.7592</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1918,31 +1918,31 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7622</v>
+        <v>-0.7592</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1573</v>
+        <v>-0.1579</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>C. WALDEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.344</v>
+        <v>-2.5471</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9566</v>
+        <v>-0.1155</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3873</v>
+        <v>-2.4316</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2759</v>
+        <v>-1.2405</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2338</v>
+        <v>0.5572</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0422</v>
+        <v>-1.7977</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6451</v>
+        <v>1.2483</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6825</v>
+        <v>1.003</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>0.2453</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6308</v>
+        <v>-2.4888</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5513</v>
+        <v>-0.4458</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0795</v>
+        <v>-2.043</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.3066</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3115</v>
+        <v>-0.1769</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2102</v>
+        <v>-0.1297</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. WALDEN</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5111</v>
+        <v>-2.6894</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7914</v>
+        <v>-0.3624</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7197</v>
+        <v>-2.3269</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2475</v>
+        <v>-1.773</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5570000000000001</v>
+        <v>-0.0228</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8045</v>
+        <v>-1.7501</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2704</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0146</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2558</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5179</v>
+        <v>-2.4599</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4576</v>
+        <v>0.0568</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0603</v>
+        <v>-2.5168</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2636</v>
+        <v>-0.1244</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8861</v>
+        <v>0.4757</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3775</v>
+        <v>-0.6002</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5463</v>
+        <v>-1.2472</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>-0.387</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.639</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5767</v>
+        <v>-3.9006</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1278</v>
+        <v>-2.1763</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4489</v>
+        <v>-1.7242</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3356</v>
+        <v>0.3264</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7159</v>
+        <v>2.7006</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3803</v>
+        <v>-2.3742</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8645</v>
+        <v>1.8284</v>
       </c>
       <c r="K22" t="n">
-        <v>3.3626</v>
+        <v>3.3332</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5289</v>
+        <v>-1.502</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2238</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5898</v>
+        <v>-0.5903</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8135</v>
+        <v>0.4999</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.996</v>
+        <v>-4.1183</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6325</v>
+        <v>-0.6471</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3635</v>
+        <v>-3.4712</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4691</v>
+        <v>-0.4668</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4184</v>
+        <v>-0.4193</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0506</v>
+        <v>-0.0475</v>
       </c>
       <c r="J23" t="n">
-        <v>0.919</v>
+        <v>0.9093</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3219</v>
+        <v>0.3135</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.388</v>
+        <v>-1.3761</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2075</v>
+        <v>-0.3344</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4174</v>
+        <v>-0.4182</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2099</v>
+        <v>0.0838</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2365</v>
+        <v>-4.2953</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6355</v>
+        <v>-0.6644</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.601</v>
+        <v>-3.6308</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.2095</v>
+        <v>-4.2094</v>
       </c>
       <c r="H24" t="n">
-        <v>2.1558</v>
+        <v>2.1542</v>
       </c>
       <c r="I24" t="n">
-        <v>-6.3653</v>
+        <v>-6.3636</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3716</v>
+        <v>0.3441</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7707</v>
+        <v>2.7579</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.3991</v>
+        <v>-2.4138</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.581</v>
+        <v>-4.5535</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.9662</v>
+        <v>-3.9497</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0931</v>
+        <v>-0.1557</v>
       </c>
       <c r="T24" t="n">
-        <v>0.127</v>
+        <v>0.1297</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2202</v>
+        <v>-0.2854</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="25">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0194</v>
+        <v>-5.0795</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.7679</v>
+        <v>-4.7007</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2514</v>
+        <v>-0.3787</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.0044</v>
+        <v>-1.0112</v>
       </c>
       <c r="H25" t="n">
-        <v>1.925</v>
+        <v>1.9189</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.9294</v>
+        <v>-2.9301</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5672</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5558</v>
+        <v>2.5371</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.9886</v>
+        <v>-2.0042</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5716</v>
+        <v>-1.5441</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9408</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1588</v>
+        <v>-0.1985</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7984</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.4824</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.5357</v>
+        <v>-5.239</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.3417</v>
+        <v>-4.2689</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.194</v>
+        <v>-0.9701</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.2647</v>
+        <v>-5.2742</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.5063</v>
+        <v>-1.5159</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.7584</v>
+        <v>-3.7583</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.2931</v>
+        <v>-3.3302</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.3791</v>
+        <v>-1.4004</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.914</v>
+        <v>-1.9298</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.9716</v>
+        <v>-1.9441</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.8444</v>
+        <v>-1.8285</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3617</v>
+        <v>-0.0558</v>
       </c>
       <c r="T26" t="n">
-        <v>0.127</v>
+        <v>0.2481</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4888</v>
+        <v>-0.3039</v>
       </c>
       <c r="V26" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W26" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-34.9491</v>
+        <v>-34.9477</v>
       </c>
       <c r="E27" t="n">
-        <v>-17.3477</v>
+        <v>-17.6388</v>
       </c>
       <c r="F27" t="n">
-        <v>-17.6013</v>
+        <v>-17.3085</v>
       </c>
       <c r="G27" t="n">
-        <v>-21.2062</v>
+        <v>-21.1915</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1837</v>
+        <v>1.1509</v>
       </c>
       <c r="I27" t="n">
-        <v>-22.3901</v>
+        <v>-22.3421</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.01060000000000016</v>
+        <v>-0.2296</v>
       </c>
       <c r="K27" t="n">
-        <v>5.601</v>
+        <v>5.464399999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>-5.6117</v>
+        <v>-5.694</v>
       </c>
       <c r="M27" t="n">
-        <v>-21.1955</v>
+        <v>-20.962</v>
       </c>
       <c r="N27" t="n">
-        <v>-4.417300000000001</v>
+        <v>-4.3137</v>
       </c>
       <c r="O27" t="n">
-        <v>-16.7784</v>
+        <v>-16.6481</v>
       </c>
       <c r="P27" t="n">
-        <v>-9.073500000000001</v>
+        <v>-9.105399999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>-19.2809</v>
+        <v>-19.3488</v>
       </c>
       <c r="R27" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.1342</v>
+        <v>-1.1381</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.2703</v>
+        <v>-1.2575</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1358</v>
+        <v>0.1193</v>
       </c>
       <c r="V27" t="n">
-        <v>-3.5352</v>
+        <v>-3.5124</v>
       </c>
       <c r="W27" t="n">
-        <v>3.2139</v>
+        <v>3.197</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.749</v>
+        <v>-6.7095</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104618_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104618_W18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-3.197</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104618_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-6.7095</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
